--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A340"/>
+  <dimension ref="A1:A316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,49 +557,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
+          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
         </is>
       </c>
     </row>
@@ -669,35 +669,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2105326</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
+          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
+          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/india/maharashtra-to-provide-free-cancer-vaccines-for-girls-aged-0-14-amid-rising-cases-article-118653086</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-to-form-leprosy-eradication-committee--106388</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/01/bom39-mh-ld-elephant-minister.html</t>
+          <t>https://www.ptinews.com/detail/states/Efforts-on-to-bring-back-%E2%80%98Mahadevi%E2%80%99-from-Vantara--Maharashtra-minister/2784129</t>
         </is>
       </c>
     </row>
@@ -711,2100 +711,1932 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-to-form-leprosy-eradication-committee--106388</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-approves-inter-and-intra-district-transfers-for-chos-based-on-their-requests-23558258</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-approves-inter-and-intra-district-transfers-for-chos-based-on-their-requests-23558258</t>
+          <t>https://assamtribune.com/national/minister-abitkar-leads-the-maharashtra-governments-two-week-organ-donation-campaign-by-filling-the-form-1587216</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/minister-abitkar-leads-the-maharashtra-governments-two-week-organ-donation-campaign-by-filling-the-form-1587216</t>
+          <t>https://ehealth.eletsonline.com/2025/02/mumbai-reports-first-suspected-gbs-case-amid-rising-cases-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://ehealth.eletsonline.com/2025/02/mumbai-reports-first-suspected-gbs-case-amid-rising-cases-in-maharashtra/</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/health-minister-prakash-abitkar-announces-one-lakh-reward-134351424.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/health-minister-prakash-abitkar-announces-one-lakh-reward-134351424.html</t>
+          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-gbs-disease-was-discussed-in-the-cabinet-meeting-health-minister-said-this-2025-01-28-1108795</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-corona-cases-health-minister-prakash-abitkar-said-do-not-panic-about-covid-19-ann-2957290</t>
+          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
+          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
+          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
+          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/state/news-4249/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/health-minister-prakash-abitkar-on-dcm-ajit-pawar-pune-hindu-hrudaysamrat-balasaheb-thakrey-aapla-dawakhana-1356102</t>
+          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
+          <t>https://marathi.abplive.com/news/health-minister-prakash-abitkar-announces-beed-district-civil-surgeon-ashok-thorat-suspended-in-vidhan-sabha-maharashtra-budget-session-marathi-news-1350939</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-prakash-abitkar-instructions-no-issue-of-the-disabled-should-be-left-unsolved-marathi-news-1358401</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/minister-prakash-abitkars-big-revelation-in-maharashtra-politics-delay-in-farmers-loan-waiver-due-to-ladki-bahin-scheme/articleshow/121847611.cms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/health-minister-prakash-abitkar-announces-beed-district-civil-surgeon-ashok-thorat-suspended-in-vidhan-sabha-maharashtra-budget-session-marathi-news-1350939</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-surprise-visit-to-hospital-anger-over-management-dispute-among-officials/articleshow/121994682.cms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
+          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/minister-prakash-abitkars-big-revelation-in-maharashtra-politics-delay-in-farmers-loan-waiver-due-to-ladki-bahin-scheme/articleshow/121847611.cms</t>
+          <t>https://mahasamvad.in/159642/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/prakash-abitkar-on-hospital-1357379</t>
+          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-guardian-minister-prakash-abitkar-has-categorically-stated-that-shiv-sena-is-the-largest-party-in-the-mahayuti-in-the-district-marathi-news-update-1372685</t>
+          <t>https://mahasamvad.in/155891/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
+          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-suggestions-to-strengthen-healthcare-services-at-the-high-level-meeting-mumbai-print-news-zws-70-5104660/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
+          <t>https://mahasamvad.in/154597/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159642/</t>
+          <t>https://mahasamvad.in/175693/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-warning-to-karnataka-from-the-height-of-almatti-maharashtra-marathi-news-update-1357399</t>
+          <t>https://www.mahasamvad.in/170012/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170017/</t>
+          <t>https://www.loksatta.com/kolhapur/kalhapur-prakash-abitkar-calls-for-unity-in-celebrating-independence-day-with-diverse-event-over-veg-nonveg-debate-rds-00-5306948/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
+          <t>https://mahasamvad.in/153447/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155891/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/hpv-vaccination-in-maharashtra-health-minister-prakash-abitkar-informed-that-cancer-vaccine-will-be-given-free-to-girls-up-to-age-of-14-maharashtra-news-mhs25030200577</t>
+          <t>https://mahasamvad.in/157284/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/health-minister-prakashrao-abitkar-on-dinanath-mangeshkar-hospital-tanisha-bhise-death-case-gkt-96-4997347/</t>
+          <t>https://mahasamvad.in/166367/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154597/</t>
+          <t>https://www.mahasamvad.in/157564/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175693/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/170012/</t>
+          <t>https://marathi.abplive.com/news/politics/prakashrao-abitkar-says-a-reward-of-one-lakh-will-be-given-to-informers-who-tip-off-that-pregnancy-diagnosis-is-in-progress-a-big-announcement-by-the-health-minister-prakashrao-abitkar-in-kolhapur-maharashtra-politics-marathi-news-1340501</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-minister-prakash-abitkar-takes-senior-citizens-on-air-trip-unique-guru-purnima-initiative-vsd-99-5224693/</t>
+          <t>https://mahasamvad.in/173263/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153447/</t>
+          <t>https://www.mahasamvad.in/167252/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157284/</t>
+          <t>https://mahasamvad.in/157463/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/156822/</t>
+          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166367/</t>
+          <t>https://mahasamvad.in/172391/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/157564/</t>
+          <t>https://mahasamvad.in/174644/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
+          <t>https://mahasamvad.in/173559/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173263/</t>
+          <t>https://mahasamvad.in/173259/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/167252/</t>
+          <t>https://mahasamvad.in/166403/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-gave-an-explanation-in-the-legislative-council-phm-00-5212114/</t>
+          <t>https://mahasamvad.in/154283/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/cashless-treatment-in-hospital-maharashtra-cashless-treatment-up-to-rs-1-lakh-for-accident-victims-big-decision-of-the-health-department-of-maharashtra-1354955</t>
+          <t>https://mahasamvad.in/174701/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157463/</t>
+          <t>https://mahasamvad.in/174852/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
+          <t>https://mahasamvad.in/168889/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172391/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174644/</t>
+          <t>https://mahasamvad.in/168802/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164322/</t>
+          <t>https://mahasamvad.in/154909/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173559/</t>
+          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162788/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173259/</t>
+          <t>https://www.loksatta.com/politics/in-kolhapur-disagreement-among-ministers-over-shaktipeeth-highway-project-print-politics-news-asj-82-4885640/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158717/</t>
+          <t>https://mahasamvad.in/151861/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166403/</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172859/</t>
+          <t>https://maharashtradesha.com/health-minister-prakash-abitkar-on-dinanath-mangeshkar-hospital-probe/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154283/</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174701/</t>
+          <t>https://maharashtranews1.com/Based-on-the-Ideal-Shed-campaign--now-the-district-has-a-Clean---Beautiful-House-campaign-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165634/</t>
+          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-news-health-minister-prakashrao-abitkar-orders-action-in-case-of-womans-death-during-childbirth-police-will-conduct-investigation-today-will-examine-cctv-along-with-statements-from-nurses-and-doctors-1352627</t>
+          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
+          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168735/</t>
+          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174852/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/health-minister-prakash-abitkar-takes-oath-for-organ-donation-various-awareness-activities-in-the-state/128039/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168889/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
+          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174294/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168802/</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154909/</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
+          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151861/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
+          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
+          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
+          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
+          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
+          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/health-policy-for-the-first-time-in-the-history-of-the-state-minister-prakash-abitkar/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-deenanath-mangeshkar-hospital-demands-20-lakhs-before-treatment-pregnant-woman-loses-life-live-updates-in-marathi-pmw-88-4997202/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
+          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/corona-wave-update-maharashtra-health-minister-prakash-abitkar-statement-1414124.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
+          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-beed-district-surgeon-suspended-over-irregularities-in-medicine-procurement-during-covid-19-enn25032502769</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3526640-the-controversy-of-mahadevi-a-36-year-old-elephants-journey-from-kolhapur-to-gujarat</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
+          <t>https://ndtv.in/health/1st-suspected-gbs-case-surfaced-in-mumbai-know-how-to-prevent-it-7662749</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
+          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-7825621</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
+          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
+          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
+          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://ndtv.in/health/1st-suspected-gbs-case-surfaced-in-mumbai-know-how-to-prevent-it-7662749</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-three-leaders-have-six-districts-two-kolhapur-and-mumbai-have-to-ministers-of-guardian-ministry-devendra-fadnavis-masterstroke-to-avoid-conflict-marathi-news-1339325</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-1-june-2025-sunday-latest-marathi-news-update-maharashtra-politics-marathi-news-1362038</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-beed-santosh-deshmukh-case-maharashtra-politics-malegaon-sahakari-sakhar-karkhana-election-2025-1365817</t>
+          <t>https://impressivetimes.com/latest/news-3192/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/congress-leader-sharangdhar-deshmukh-and-many-bjp-formor-corporaters-joins-shiv-sena-in-kolhapur/articleshow/122053302.cms</t>
+          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/on-eknath-shinde-birthday-deputy-chief-minister-announces-medical-aid-cell-in-the-state-mangesh-chivte-takes-responsibility-1343588</t>
+          <t>https://www.punekarnews.in/pune-ajit-pawar-inaugurates-43-aapla-davakhana-clinics-lays-foundation-for-state-family-welfare-building/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-devendra-fadnavis-first-reaction-about-mahadevi-hattini-case/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/cm-devendra-fadnavis-pm-awas-yojana/</t>
+          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/kolhapurkars-should-attend-yuvashakti-dahi-handi-in-large-numbers-kha-dhananjay-mahadik/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
+          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
+          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
+          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
+          <t>https://mahasamvad.in/164322/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
+          <t>https://mahasamvad.in/170909/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
+          <t>https://mahasamvad.in/170610/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
+          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2105326</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
+          <t>https://mahasamvad.in/160560/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
+          <t>https://mahasamvad.in/173688/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
+          <t>https://www.mahasamvad.in/page/523/?m=0</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-screen-over-1-66-crore-children-in-special-drive-101740770920444.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/04/19/rs-1-lakh-cashless-treatment-for-accident-victims-maharashtra-governments-new-move/</t>
+          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3548680-sanjeevani-transforming-cancer-care-through-unity-and-awareness</t>
+          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
+          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-ajit-pawar-inaugurates-43-aapla-davakhana-clinics-lays-foundation-for-state-family-welfare-building/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/rs-1-lakh-cash-reward-for-informants-decoys-helping-bust-illegal-sex-determination-abortion-rackets/articleshow/117612427.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2105326</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170909/</t>
+          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170610/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-farmers-to-hold-state-wide-march-in-mumbai-on-march-12-against-shaktipeeth-highway-enn25030105581</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
+          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160560/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173688/</t>
+          <t>https://www.healthcareradius.in/clinical/covid-corner/gbs-claims-first-victim-in-pune-amid-rising-cases-central-team-dispatched-virus-outbreak-gbsvirus</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/523/?m=0</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-big-statement-on-ladki-bahin-yojana/articleshow/120848813.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
+          <t>https://marathi.abplive.com/news/pune/pune-tanisha-bhise-death-case-four-member-committee-to-investigate-dinanath-hospital-prakash-abitkar-madhuri-misal-decision-maharashtra-marathi-news-1352646</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-heavy-rain-disrupts-daily-life-significant-damage-to-agriculture/articleshow/121814826.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/bargain-and-delay-in-getting-horses-save-28-tourist-from-walking-into-pahalgam-terror-site/articleshow/120580319.cms</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
+          <t>https://mahasamvad.in/172749/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
+          <t>https://mahasamvad.in/173717/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
+          <t>https://mahasamvad.in/172235/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
+          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
+          <t>https://zeenews.india.com/hindi/health/first-case-of-guillain-barre-syndrome-in-mumbai-total-gbs-patient-number-180-maharashtra/2637580</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
+          <t>https://mahasamvad.in/165634/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
+          <t>https://mahasamvad.in/173797/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
+          <t>https://mahasamvad.in/175714/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
+          <t>https://mahasamvad.in/163359/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
+          <t>https://mahasamvad.in/155268/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.healthcareradius.in/clinical/covid-corner/gbs-claims-first-victim-in-pune-amid-rising-cases-central-team-dispatched-virus-outbreak-gbsvirus</t>
+          <t>https://livemarathi.in/health-policy-for-the-first-time-in-the-history-of-the-state-minister-prakash-abitkar/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/over-14-500-women-detected-with-cancer-like-symptoms-post-screening-in-maharashtra-hingoli-1787139</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-government-rs-123-crore-mortuary-van-project-132-new-vehicles-unused-2693784-2025-03-15</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/more-that-12k-children-died-in-maharashtra-between-april-last-year-and-february-2025-minister-3619100</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
+          <t>https://mahasamvad.in/158746/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
+          <t>https://mahasamvad.in/172859/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
+          <t>https://mahasamvad.in/166821/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172749/</t>
+          <t>https://mahasamvad.in/155119/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173717/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172235/</t>
+          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-breaking-news-live-updates-marathwada-farmers-death-shirish-valsangkar-suscide-case-raj-thackeray-uddhav-thackeray-alliance-gold-price-today-22-april-2025-asc-95-5037779/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/two-covid-patients-die-of-comorbidities-at-mumbai-kem-hospital-health-minister-prakash-abitkar-says-no-need-to-panic-maharashtra-news-mhs25052003840</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173797/</t>
+          <t>https://nenow.in/national/kolhapur-residents-hold-silent-march-seek-return-of-elephant-mahadevi-from-gujarats-vantara.html</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163359/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155268/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
+          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158746/</t>
+          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166821/</t>
+          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155119/</t>
+          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170747/</t>
+          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
+          <t>https://www.dainikprabhat.com/maharashtra-news-hindustani-bhau-madhuri-elephant-kolhapur-vantara/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
+          <t>https://ddnews.gov.in/en/maharashtra-records-second-suspected-gbs-death-cases-rise-to-127/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/daga-hospitals-nicu-ranked-best-in-maharashtra-at-state-health-awards/articleshow/120074378.cms</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
+          <t>https://mahasamvad.in/174294/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
+          <t>https://mahasamvad.in/175429/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/mission-madhuri-elephant-2-lakh-4-thousand-421-people-signatures-in-satej-patil-campaign-public-outrage-will-reach-the-president-marathi-news-update-1374246</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
+          <t>https://www.expresshealthcare.in/amp/news/narayana-health-srcc-childrens-hospital-observes-world-child-obesity-day-2025-in-collaboration-with-gen-xl-foundation/449213/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/maharashtra-news-hindustani-bhau-madhuri-elephant-kolhapur-vantara/</t>
+          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/daga-hospitals-nicu-ranked-best-in-maharashtra-at-state-health-awards/articleshow/120074378.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
+          <t>https://mahasamvad.in/170017/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175429/</t>
+          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/81/?m=0</t>
+          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/37/?m=0</t>
+          <t>https://mahasamvad.in/151398/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
+          <t>https://mahasamvad.in/154371/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
+          <t>https://mahasamvad.in/161521/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
+          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-15-march-2025-eknath-shinde-ajit-pawar-maharashtra-politics-marathi-news-1351019</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
+          <t>https://mahasamvad.in/174716/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/probable-list-of-guardian-minister-announced-dhananjay-munden-is-responsible-for-this-district-1336522.html</t>
+          <t>https://mahasamvad.in/172498/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-sports-crime-national-international-lifestyle-news-898945.html</t>
+          <t>https://mahasamvad.in/171744/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-businessman-son-died-in-horrifying-accident-with-car-expensive-bike-and-helmet-broken-into-pieces/articleshow/120491249.cms</t>
+          <t>https://mahasamvad.in/171817/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/jotiba-yatra-in-kolhapur-has-begun-from-today/articleshow/120201841.cms</t>
+          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
+          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
+          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151398/</t>
+          <t>https://mahasamvad.in/167140/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154371/</t>
+          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
+          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/154371/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161521/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-what-is-the-inside-of-the-kolhapur-circuit-bench-like-first-glimpse-of-the-state-of-the-art-court-room-1377632</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
+          <t>https://mahasamvad.in/174988/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174716/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-issues-directives-to-strengthen-healthcare-system/121275010</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172498/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/farmers-protest-against-nagpur-goa-shaktipeeth-highway-vow-to-block-land-acquisition/118975130</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171744/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167140/</t>
+          <t>https://www.oneindia.com/india/over-14-500-women-show-cancer-like-symptoms-after-screening-drive-in-hingoli-7797015.html</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
+          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
+          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/chief-justice-of-india-bhushan-gavai-says-kolhapur-bench-is-a-milestone-for-social-and-economic-justice-in-the-country-will-soon-be-converted-into-a-bench-1377738</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-what-is-the-inside-of-the-kolhapur-circuit-bench-like-first-glimpse-of-the-state-of-the-art-court-room-1377632</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/174988/</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/farmers-protest-against-nagpur-goa-shaktipeeth-highway-vow-to-block-land-acquisition/118975130</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/maharashtra/more-than-270-crores-due-from-mahatma-phule-and-ayushman-yojana-affiliated-hospitals-from-the-maharashtra-mahayuti-government-1352831</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>https://m.thewire.in/article/ptiprnews/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/amp?utm=relatedarticles</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>https://www.punekarnews.in/500-surgeries-delayed-at-punes-sassoon-hospital-as-nurses-strike-in-maharashtra-government-hospitals-enters-sixth-day/</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>https://ahmednagarlive24.com/ahilyanagar-news/more-facilities-at-the-100-bed-ghulewadi-rural-hospital-started-through-the-efforts-of-former-minister-balasaheb-thorat-asst-satyajit-tambe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278515631/maharashtra-cji-bhushan-gavai-inaugurates-fifth-bench-of-bombay-hc-at-kolhapur</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/arogya-mitras-to-go-on-indefinite-statewide-strike-from-feb-12-101737405442305.html</t>
+          <t>https://mahasamvad.in/158717/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A316"/>
+  <dimension ref="A1:A311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,42 +459,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-prakash-abitkar-acknowledges-challenges-in-fund-availability-due-to-ladki-bahin/articleshow/120857765.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-assures-policy-for-rare-disorder-after-parents-protest-outside-mantralaya-101745351008595.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-prakash-abitkar-acknowledges-challenges-in-fund-availability-due-to-ladki-bahin/articleshow/120857765.cms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/law-to-empower-health-officials-to-take-action-against-those-contaminating-drinking-water-on-cards-abitkar/articleshow/117867170.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/new-app-to-ensure-transparency-accountability-in-mjpjay-scheme-abitkar-101746298903204.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/new-app-to-ensure-transparency-accountability-in-mjpjay-scheme-abitkar-101746298903204.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/law-to-empower-health-officials-to-take-action-against-those-contaminating-drinking-water-on-cards-abitkar/articleshow/117867170.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/esic-hospital-in-mumbai-to-open-in-dec-says-maharashtra-public-health-minister-prakash-abitkar/articleshow/122256849.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-orders-closure-of-258-pvt-hosps-over-violations-101752780027844.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-orders-closure-of-258-pvt-hosps-over-violations-101752780027844.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/esic-hospital-in-mumbai-to-open-in-dec-says-maharashtra-public-health-minister-prakash-abitkar/articleshow/122256849.cms</t>
         </is>
       </c>
     </row>
@@ -536,112 +536,112 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/cmo-denies-staying-3-2k-cr-contract-of-ex-health-minister/articleshow/118654151.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-launches-second-probe-into-financial-transactions-at-regional-mental-hospital-101736964694048.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-launches-second-probe-into-financial-transactions-at-regional-mental-hospital-101736964694048.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
+          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-ask-centre-to-include-thalassemia-in-national-health-scheme-maharashtra-health-minister-prakash-abitkar-23587287</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/contaminated-well-suspected-in-gbs-spike-pune-civic-body-now-supplies-clean-water-through-tankers-101738005488804.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-set-up-state-level-committee-for-effective-leprosy-eradication-says-maharashtra-health-minister-prakash-abitkar-23584820</t>
+          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-ask-centre-to-include-thalassemia-in-national-health-scheme-maharashtra-health-minister-prakash-abitkar-23587287</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cap-diagnostic-test-prices-soon-23502807</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/contaminated-well-suspected-in-gbs-spike-pune-civic-body-now-supplies-clean-water-through-tankers-101738005488804.html</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-proposes-to-amend-bombay-nursing-home-act-health-dept-to-hire-legal-firm/articleshow/121275842.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/charitable-hospitals-must-comply-with-govt-health-scheme-gr-minister/articleshow/122866818.cms</t>
+          <t>https://impressivetimes.com/state/news-4249/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cap-diagnostic-test-prices-soon-23502807</t>
+          <t>https://www.etvbharat.com/en/!state/gbs-cases-in-pune-linked-to-suspected-water-contamination-says-maharashtra-minister-enn25012706765</t>
         </is>
       </c>
     </row>
@@ -655,35 +655,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/efforts-on-to-bring-back-%E2%80%98mahadevi%E2%80%99-from-vantara:-maharashtra-minister/2784707</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
+          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
+          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
+          <t>https://www.ptinews.com/detail/states/Efforts-on-to-bring-back-%E2%80%98Mahadevi%E2%80%99-from-Vantara--Maharashtra-minister/2784129</t>
         </is>
       </c>
     </row>
@@ -697,105 +697,105 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/states/Efforts-on-to-bring-back-%E2%80%98Mahadevi%E2%80%99-from-Vantara--Maharashtra-minister/2784129</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-approves-inter-and-intra-district-transfers-for-chos-based-on-their-requests-23558258</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/bt-tv/video/alert-after-covid-cases-rise-maharashtra-health-minister-no-need-to-panic-477235-2025-05-21</t>
+          <t>https://assamtribune.com/national/minister-abitkar-leads-the-maharashtra-governments-two-week-organ-donation-campaign-by-filling-the-form-1587216</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-approves-inter-and-intra-district-transfers-for-chos-based-on-their-requests-23558258</t>
+          <t>https://ehealth.eletsonline.com/2025/02/mumbai-reports-first-suspected-gbs-case-amid-rising-cases-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/minister-abitkar-leads-the-maharashtra-governments-two-week-organ-donation-campaign-by-filling-the-form-1587216</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/health-minister-prakash-abitkar-announces-one-lakh-reward-134351424.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://ehealth.eletsonline.com/2025/02/mumbai-reports-first-suspected-gbs-case-amid-rising-cases-in-maharashtra/</t>
+          <t>https://www.deshbandhu.co.in/states/there-are-197-patients-of-guillain-barre-syndrome-in-maharashtra-health-minister-prakash-abitkar-534784-1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/health-minister-prakash-abitkar-announces-one-lakh-reward-134351424.html</t>
+          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
+          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
+          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
+          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
+          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
+          <t>https://marathi.abplive.com/news/pune/health-minister-prakash-abitkar-on-dcm-ajit-pawar-pune-hindu-hrudaysamrat-balasaheb-thakrey-aapla-dawakhana-1356102</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
+          <t>https://www.etvbharat.com/mr/!state/gbs-disease-does-not-cause-death-health-minister-prakash-abitkar-clarifies-in-pune-maharashtra-news-mhs25012706012</t>
         </is>
       </c>
     </row>
@@ -816,28 +816,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/health-minister-prakash-abitkar-announces-beed-district-civil-surgeon-ashok-thorat-suspended-in-vidhan-sabha-maharashtra-budget-session-marathi-news-1350939</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
+          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-told-the-legislative-assembly-that-the-process-of-drafting-the-law-is-underway-pune-print-news-phm-00-5219873/</t>
         </is>
       </c>
     </row>
@@ -851,133 +851,133 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-surprise-visit-to-hospital-anger-over-management-dispute-among-officials/articleshow/121994682.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-big-statement-on-ladki-bahin-yojana/articleshow/120848813.cms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-surprise-visit-to-hospital-anger-over-management-dispute-among-officials/articleshow/121994682.cms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159642/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
+          <t>https://mahasamvad.in/159642/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155891/</t>
+          <t>https://mahasamvad.in/170017/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-suggestions-to-strengthen-healthcare-services-at-the-high-level-meeting-mumbai-print-news-zws-70-5104660/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-guidance-during-the-agriculture-department-meeting-sud-02-5087323/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154597/</t>
+          <t>https://mahasamvad.in/155891/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175693/</t>
+          <t>https://www.etvbharat.com/mr/!state/hpv-vaccination-in-maharashtra-health-minister-prakash-abitkar-informed-that-cancer-vaccine-will-be-given-free-to-girls-up-to-age-of-14-maharashtra-news-mhs25030200577</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/170012/</t>
+          <t>https://www.mymahanagar.com/maharashtra/mahadevi-elephant-in-nandani-will-return-minister-prakash-abitkar-gave-information-about-legal-process/907779/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kalhapur-prakash-abitkar-calls-for-unity-in-celebrating-independence-day-with-diverse-event-over-veg-nonveg-debate-rds-00-5306948/</t>
+          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153447/</t>
+          <t>https://mahasamvad.in/154597/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
+          <t>https://mahasamvad.in/175693/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157284/</t>
+          <t>https://www.mahasamvad.in/170012/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166367/</t>
+          <t>https://mahasamvad.in/153447/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/157564/</t>
+          <t>https://mahasamvad.in/157284/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
+          <t>https://mahasamvad.in/156822/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/prakashrao-abitkar-says-a-reward-of-one-lakh-will-be-given-to-informers-who-tip-off-that-pregnancy-diagnosis-is-in-progress-a-big-announcement-by-the-health-minister-prakashrao-abitkar-in-kolhapur-maharashtra-politics-marathi-news-1340501</t>
+          <t>https://www.mahasamvad.in/157564/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173263/</t>
+          <t>https://mahasamvad.in/166367/</t>
         </is>
       </c>
     </row>
@@ -991,1652 +991,1617 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
+          <t>https://mahasamvad.in/173263/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157463/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
+          <t>https://mahasamvad.in/157463/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172391/</t>
+          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174644/</t>
+          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173559/</t>
+          <t>https://mahasamvad.in/164322/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173259/</t>
+          <t>https://mahasamvad.in/173559/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166403/</t>
+          <t>https://www.etvbharat.com/mr/!state/vantara-ready-to-return-mahadevi-elephant-if-court-orders-guardian-minister-prakash-abitkar-maharashtra-news-mhs25080105913</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154283/</t>
+          <t>https://mahasamvad.in/172391/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174701/</t>
+          <t>https://mahasamvad.in/174644/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
+          <t>https://mahasamvad.in/166403/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174852/</t>
+          <t>https://mahasamvad.in/165634/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168889/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
+          <t>https://mahasamvad.in/158717/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168802/</t>
+          <t>https://www.tv9marathi.com/videos/covid-cases-rise-singapore-hongkong-india-alert-mumbai-health-minister-prakash-abitkar-statement-1408354.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154909/</t>
+          <t>https://mahasamvad.in/168735/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
+          <t>https://mahasamvad.in/172859/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
+          <t>https://mahasamvad.in/174852/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/in-kolhapur-disagreement-among-ministers-over-shaktipeeth-highway-project-print-politics-news-asj-82-4885640/</t>
+          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151861/</t>
+          <t>https://mahasamvad.in/154283/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
+          <t>https://mahasamvad.in/174701/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/health-minister-prakash-abitkar-on-dinanath-mangeshkar-hospital-probe/</t>
+          <t>https://mahasamvad.in/158289/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
+          <t>https://mahasamvad.in/168889/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Based-on-the-Ideal-Shed-campaign--now-the-district-has-a-Clean---Beautiful-House-campaign-</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
+          <t>https://mahasamvad.in/168802/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
+          <t>https://mahasamvad.in/175714/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
+          <t>https://mahasamvad.in/174294/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
+          <t>https://mahasamvad.in/154909/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/health-minister-prakash-abitkar-takes-oath-for-organ-donation-various-awareness-activities-in-the-state/128039/</t>
+          <t>https://mahasamvad.in/151398/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
+          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
+          <t>https://mahasamvad.in/151861/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
+          <t>https://maharashtradesha.com/health-minister-prakash-abitkar-on-dinanath-mangeshkar-hospital-probe/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
+          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
+          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
+          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
+          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
+          <t>https://www.tv9marathi.com/videos/corona-wave-update-maharashtra-health-minister-prakash-abitkar-statement-1414124.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
+          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
+          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
+          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
+          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
+          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/cmo-denies-staying-3-2k-cr-contract-of-ex-health-minister/articleshow/118654151.cms</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/charitable-hospitals-must-comply-with-govt-health-scheme-gr-minister/articleshow/122866818.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
+          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3526640-the-controversy-of-mahadevi-a-36-year-old-elephants-journey-from-kolhapur-to-gujarat</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://ndtv.in/health/1st-suspected-gbs-case-surfaced-in-mumbai-know-how-to-prevent-it-7662749</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
+          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-7825621</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
+          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/vikhe-patil-to-irrigation-dept-study-concerns-on-almatti-dam/articleshow/121323044.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
+          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/congress-leader-sharangdhar-deshmukh-and-many-bjp-formor-corporaters-joins-shiv-sena-in-kolhapur/articleshow/122053302.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-shinde-shivsena-cabinet-ministers-get-angry-on-devendra-fadnavis-cmo-office-over-pa-and-osd-appointment-delay-1343532</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/on-eknath-shinde-birthday-deputy-chief-minister-announces-medical-aid-cell-in-the-state-mangesh-chivte-takes-responsibility-1343588</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
+          <t>https://livemarathi.in/kolhapurkars-should-attend-yuvashakti-dahi-handi-in-large-numbers-kha-dhananjay-mahadik/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
+          <t>https://www.timemaharashtra.com/trending/nandani-math-mahadevi-elephant-will-nandani-maths-madhuri-return-what-did-vantaras-ceo-say/127830/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
+          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-proposes-to-amend-bombay-nursing-home-act-health-dept-to-hire-legal-firm/articleshow/121275842.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/news-3192/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-ajit-pawar-inaugurates-43-aapla-davakhana-clinics-lays-foundation-for-state-family-welfare-building/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
+          <t>https://impressivetimes.com/latest/news-3192/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
+          <t>https://www.devdiscourse.com/article/business/3548680-sanjeevani-transforming-cancer-care-through-unity-and-awareness</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
+          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164322/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170909/</t>
+          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170610/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2105326</t>
+          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
+          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160560/</t>
+          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173688/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/523/?m=0</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
+          <t>https://mahasamvad.in/170909/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
+          <t>https://mahasamvad.in/170610/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
+          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
+          <t>https://mahasamvad.in/160560/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
+          <t>https://mahasamvad.in/157898/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
+          <t>https://mahasamvad.in/173688/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
+          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
+          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
+          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2105326</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.healthcareradius.in/clinical/covid-corner/gbs-claims-first-victim-in-pune-amid-rising-cases-central-team-dispatched-virus-outbreak-gbsvirus</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
+          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-big-statement-on-ladki-bahin-yojana/articleshow/120848813.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-tanisha-bhise-death-case-four-member-committee-to-investigate-dinanath-hospital-prakash-abitkar-madhuri-misal-decision-maharashtra-marathi-news-1352646</t>
+          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
+          <t>https://www.deccanherald.com/india/maharashtra/more-that-12k-children-died-in-maharashtra-between-april-last-year-and-february-2025-minister-3619100</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-heavy-rain-disrupts-daily-life-significant-damage-to-agriculture/articleshow/121814826.cms</t>
+          <t>https://mahasamvad.in/172749/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/bargain-and-delay-in-getting-horses-save-28-tourist-from-walking-into-pahalgam-terror-site/articleshow/120580319.cms</t>
+          <t>https://mahasamvad.in/173717/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172749/</t>
+          <t>https://mahasamvad.in/172235/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173717/</t>
+          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172235/</t>
+          <t>https://mahasamvad.in/173797/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
+          <t>https://mahasamvad.in/163359/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/health/first-case-of-guillain-barre-syndrome-in-mumbai-total-gbs-patient-number-180-maharashtra/2637580</t>
+          <t>https://mahasamvad.in/155268/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165634/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173797/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175714/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163359/</t>
+          <t>https://mahasamvad.in/158746/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155268/</t>
+          <t>https://mahasamvad.in/166821/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/health-policy-for-the-first-time-in-the-history-of-the-state-minister-prakash-abitkar/</t>
+          <t>https://mahasamvad.in/155119/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-government-rs-123-crore-mortuary-van-project-132-new-vehicles-unused-2693784-2025-03-15</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158746/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172859/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166821/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155119/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
+          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
+          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
+          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
+          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
+          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://nenow.in/national/kolhapur-residents-hold-silent-march-seek-return-of-elephant-mahadevi-from-gujarats-vantara.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
+          <t>https://mahasamvad.in/175429/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/12k-kid-deaths-in-11-months/articleshow/122305129.cms</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/maharashtra-news-hindustani-bhau-madhuri-elephant-kolhapur-vantara/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/maharashtra-records-second-suspected-gbs-death-cases-rise-to-127/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/daga-hospitals-nicu-ranked-best-in-maharashtra-at-state-health-awards/articleshow/120074378.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
+          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174294/</t>
+          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175429/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-businessman-son-died-in-horrifying-accident-with-car-expensive-bike-and-helmet-broken-into-pieces/articleshow/120491249.cms</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
+          <t>https://www.etvbharat.com/mr/!state/shahu-maharaj-jayanti-celebrated-with-great-enthusiasm-in-kolhapur-mp-shahu-maharaj-chhatrapati-and-sharad-pawar-pay-tribute-to-shahu-maharaj-maharashtra-news-mhs25062605058</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-farmers-question-mahayuti-government-over-nagpur-goa-shaktipeeth-highway-bam92</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.expresshealthcare.in/amp/news/narayana-health-srcc-childrens-hospital-observes-world-child-obesity-day-2025-in-collaboration-with-gen-xl-foundation/449213/</t>
+          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
+          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
+          <t>https://www.mahasamvad.in/154371/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
+          <t>https://dainikekmat.com/%E0%A4%B2%E0%A4%BE%E0%A4%A1%E0%A4%95%E0%A5%80-%E0%A4%AC%E0%A4%B9%E0%A5%80%E0%A4%A3%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%86%E0%A4%B0%E0%A5%8B%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%BE/96992/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
+          <t>https://mahasamvad.in/161521/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
+          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170017/</t>
+          <t>https://mahasamvad.in/174716/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
+          <t>https://mahasamvad.in/172498/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151398/</t>
+          <t>https://mahasamvad.in/171744/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154371/</t>
+          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161521/</t>
+          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
+          <t>https://www.oneindia.com/mumbai/kolhapur-rises-for-mahadevi-thousands-join-silent-march-demanding-elephants-return-from-vantara-011-7820557.html</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
+          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
+          <t>https://mahasamvad.in/167140/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174716/</t>
+          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172498/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171744/</t>
+          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171817/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
+          <t>https://deshdoot.com/maharashtra-government-announces-list-of-ministers-who-will-hoist-the-flag-on-august-15/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
+          <t>https://mahasamvad.in/174988/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167140/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-what-is-the-inside-of-the-kolhapur-circuit-bench-like-first-glimpse-of-the-state-of-the-art-court-room-1377632</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/sdma-structure-to-be-changed-to-accommodate-maharashtra-deputy-cms-3400638</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174988/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
+          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/farmers-protest-against-nagpur-goa-shaktipeeth-highway-vow-to-block-land-acquisition/118975130</t>
+          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/arogya-mitras-to-go-on-indefinite-statewide-strike-from-feb-12-101737405442305.html</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-instructs-to-make-special-arrangement-for-treatment-of-gbs-patients20250128191358/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
+          <t>https://www.bignewsnetwork.com/news/278523385/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-acrob-india</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>https://www.oneindia.com/india/over-14-500-women-show-cancer-like-symptoms-after-screening-drive-in-hingoli-7797015.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/158717/</t>
+          <t>https://mahasamvad.in/171817/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A311"/>
+  <dimension ref="A1:A334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-ask-centre-to-include-thalassemia-in-national-health-scheme-maharashtra-health-minister-prakash-abitkar-23587287</t>
         </is>
       </c>
     </row>
@@ -536,42 +536,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-launches-second-probe-into-financial-transactions-at-regional-mental-hospital-101736964694048.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-launches-second-probe-into-financial-transactions-at-regional-mental-hospital-101736964694048.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-ask-centre-to-include-thalassemia-in-national-health-scheme-maharashtra-health-minister-prakash-abitkar-23587287</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-set-up-state-level-committee-for-effective-leprosy-eradication-says-maharashtra-health-minister-prakash-abitkar-23584820</t>
         </is>
       </c>
     </row>
@@ -606,14 +606,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cap-diagnostic-test-prices-soon-23502807</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cap-diagnostic-test-prices-soon-23502807</t>
+          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/state/news-4249/</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-across-state-latest-updates-bird-flu-precautions-2025-03-01-978584</t>
         </is>
       </c>
     </row>
@@ -648,14 +648,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-across-state-latest-updates-bird-flu-precautions-2025-03-01-978584</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
         </is>
       </c>
     </row>
@@ -669,14 +669,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
+          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
+          <t>https://www.businesstoday.in/bt-tv/video/alert-after-covid-cases-rise-maharashtra-health-minister-no-need-to-panic-477235-2025-05-21</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/health-minister-prakash-abitkar-announces-one-lakh-reward-134351424.html</t>
+          <t>https://globalgreenews.com/2025/07/18/maharashtra-govt-cancels-licenses-of-258-private-hospitals-for-violations/</t>
         </is>
       </c>
     </row>
@@ -732,49 +732,49 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-corona-cases-health-minister-prakash-abitkar-said-do-not-panic-about-covid-19-ann-2957290</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
+          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-uddhav-thackeray-shiv-sena-leader-chandrahar-patil-join-mahayuti-soon-19656309</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
+          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
+          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
+          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
         </is>
       </c>
     </row>
@@ -795,49 +795,49 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/gbs-disease-does-not-cause-death-health-minister-prakash-abitkar-clarifies-in-pune-maharashtra-news-mhs25012706012</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-prakash-abitkar-instructions-no-issue-of-the-disabled-should-be-left-unsolved-marathi-news-1358401</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
+          <t>https://marathi.abplive.com/news/health-minister-prakash-abitkar-announces-beed-district-civil-surgeon-ashok-thorat-suspended-in-vidhan-sabha-maharashtra-budget-session-marathi-news-1350939</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-told-the-legislative-assembly-that-the-process-of-drafting-the-law-is-underway-pune-print-news-phm-00-5219873/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
         </is>
       </c>
     </row>
@@ -865,1741 +865,1902 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
+          <t>https://marathi.abplive.com/news/maharashtra/prakash-abitkar-on-hospital-1357379</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159642/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170017/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-guardian-minister-prakash-abitkar-has-categorically-stated-that-shiv-sena-is-the-largest-party-in-the-mahayuti-in-the-district-marathi-news-update-1372685</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-guidance-during-the-agriculture-department-meeting-sud-02-5087323/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-warning-to-karnataka-from-the-height-of-almatti-maharashtra-marathi-news-update-1357399</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155891/</t>
+          <t>https://mahasamvad.in/159642/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/hpv-vaccination-in-maharashtra-health-minister-prakash-abitkar-informed-that-cancer-vaccine-will-be-given-free-to-girls-up-to-age-of-14-maharashtra-news-mhs25030200577</t>
+          <t>https://mahasamvad.in/170017/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/mahadevi-elephant-in-nandani-will-return-minister-prakash-abitkar-gave-information-about-legal-process/907779/</t>
+          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
+          <t>https://mahasamvad.in/155891/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154597/</t>
+          <t>https://www.mymahanagar.com/maharashtra/mahadevi-elephant-in-nandani-will-return-minister-prakash-abitkar-gave-information-about-legal-process/907779/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175693/</t>
+          <t>https://mahasamvad.in/154597/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/170012/</t>
+          <t>https://mahasamvad.in/175693/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153447/</t>
+          <t>https://www.mahasamvad.in/170012/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157284/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/156822/</t>
+          <t>https://mahasamvad.in/153447/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/157564/</t>
+          <t>https://mahasamvad.in/157284/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166367/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/167252/</t>
+          <t>https://mahasamvad.in/156822/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173263/</t>
+          <t>https://mahasamvad.in/166367/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
+          <t>https://marathi.abplive.com/news/pune/pune-tanisha-bhise-death-case-four-member-committee-to-investigate-dinanath-hospital-prakash-abitkar-madhuri-misal-decision-maharashtra-marathi-news-1352646</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157463/</t>
+          <t>https://marathi.abplive.com/news/politics/prakashrao-abitkar-says-a-reward-of-one-lakh-will-be-given-to-informers-who-tip-off-that-pregnancy-diagnosis-is-in-progress-a-big-announcement-by-the-health-minister-prakashrao-abitkar-in-kolhapur-maharashtra-politics-marathi-news-1340501</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
+          <t>https://www.mahasamvad.in/167252/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
+          <t>https://www.mahasamvad.in/157564/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164322/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/cashless-treatment-in-hospital-maharashtra-cashless-treatment-up-to-rs-1-lakh-for-accident-victims-big-decision-of-the-health-department-of-maharashtra-1354955</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173559/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-instructions-phm-00-5256184/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/vantara-ready-to-return-mahadevi-elephant-if-court-orders-guardian-minister-prakash-abitkar-maharashtra-news-mhs25080105913</t>
+          <t>https://mahasamvad.in/173263/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172391/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174644/</t>
+          <t>https://mahasamvad.in/157463/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166403/</t>
+          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165634/</t>
+          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
+          <t>https://mahasamvad.in/164322/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158717/</t>
+          <t>https://mahasamvad.in/173559/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/covid-cases-rise-singapore-hongkong-india-alert-mumbai-health-minister-prakash-abitkar-statement-1408354.html</t>
+          <t>https://mahasamvad.in/172391/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168735/</t>
+          <t>https://mahasamvad.in/174644/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172859/</t>
+          <t>https://mahasamvad.in/166403/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174852/</t>
+          <t>https://mahasamvad.in/169637/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
+          <t>https://www.tarunbharat.com/prakash-abitkar-cpr-gaganbawda-dead-7-year-old-baby-pregnancy-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154283/</t>
+          <t>https://mahasamvad.in/165634/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174701/</t>
+          <t>https://mahasamvad.in/158717/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158289/</t>
+          <t>https://mahasamvad.in/168735/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168889/</t>
+          <t>https://mahasamvad.in/172859/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
+          <t>https://mahasamvad.in/174852/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168802/</t>
+          <t>https://mahasamvad.in/154283/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175714/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174294/</t>
+          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154909/</t>
+          <t>https://mahasamvad.in/174701/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151398/</t>
+          <t>https://mahasamvad.in/158289/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
+          <t>https://mahasamvad.in/168889/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
+          <t>https://mahasamvad.in/168802/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151861/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
+          <t>https://www.loksatta.com/mumbai/strict-action-against-illegal-hysterectomy-warns-health-minister-mumbai-print-news-ocd-94-5149349/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/health-minister-prakash-abitkar-on-dinanath-mangeshkar-hospital-probe/</t>
+          <t>https://mahasamvad.in/175714/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
+          <t>https://mahasamvad.in/174294/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
+          <t>https://mahasamvad.in/154909/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
+          <t>https://mahasamvad.in/151398/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
+          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
+          <t>https://mahasamvad.in/151861/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/corona-wave-update-maharashtra-health-minister-prakash-abitkar-statement-1414124.html</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
+          <t>https://maharashtranews1.com/Based-on-the-Ideal-Shed-campaign--now-the-district-has-a-Clean---Beautiful-House-campaign-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
+          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
+          <t>https://livemarathi.in/health-policy-for-the-first-time-in-the-history-of-the-state-minister-prakash-abitkar/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
+          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
+          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
+          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/cmo-denies-staying-3-2k-cr-contract-of-ex-health-minister/articleshow/118654151.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/charitable-hospitals-must-comply-with-govt-health-scheme-gr-minister/articleshow/122866818.cms</t>
+          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
+          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
+          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
+          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
+          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/cmo-denies-staying-3-2k-cr-contract-of-ex-health-minister/articleshow/118654151.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/charitable-hospitals-must-comply-with-govt-health-scheme-gr-minister/articleshow/122866818.cms</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
+          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
+          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/vikhe-patil-to-irrigation-dept-study-concerns-on-almatti-dam/articleshow/121323044.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
+          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
+          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/vikhe-patil-to-irrigation-dept-study-concerns-on-almatti-dam/articleshow/121323044.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/congress-leader-sharangdhar-deshmukh-and-many-bjp-formor-corporaters-joins-shiv-sena-in-kolhapur/articleshow/122053302.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-shinde-shivsena-cabinet-ministers-get-angry-on-devendra-fadnavis-cmo-office-over-pa-and-osd-appointment-delay-1343532</t>
+          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/on-eknath-shinde-birthday-deputy-chief-minister-announces-medical-aid-cell-in-the-state-mangesh-chivte-takes-responsibility-1343588</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/kolhapurkars-should-attend-yuvashakti-dahi-handi-in-large-numbers-kha-dhananjay-mahadik/</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-7825621</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/trending/nandani-math-mahadevi-elephant-will-nandani-maths-madhuri-return-what-did-vantaras-ceo-say/127830/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-three-leaders-have-six-districts-two-kolhapur-and-mumbai-have-to-ministers-of-guardian-ministry-devendra-fadnavis-masterstroke-to-avoid-conflict-marathi-news-1339325</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
+          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-1-june-2025-sunday-latest-marathi-news-update-maharashtra-politics-marathi-news-1362038</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-proposes-to-amend-bombay-nursing-home-act-health-dept-to-hire-legal-firm/articleshow/121275842.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/congress-leader-sharangdhar-deshmukh-and-many-bjp-formor-corporaters-joins-shiv-sena-in-kolhapur/articleshow/122053302.cms</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-all-district-guardian-ministers-full-list-with-name-1339324</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-shinde-shivsena-cabinet-ministers-get-angry-on-devendra-fadnavis-cmo-office-over-pa-and-osd-appointment-delay-1343532</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/on-eknath-shinde-birthday-deputy-chief-minister-announces-medical-aid-cell-in-the-state-mangesh-chivte-takes-responsibility-1343588</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
+          <t>https://deshdoot.com/cm-devendra-fadnavis-first-reaction-about-mahadevi-hattini-case/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
+          <t>https://livemarathi.in/kolhapurkars-should-attend-yuvashakti-dahi-handi-in-large-numbers-kha-dhananjay-mahadik/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
+          <t>https://www.timemaharashtra.com/trending/nandani-math-mahadevi-elephant-will-nandani-maths-madhuri-return-what-did-vantaras-ceo-say/127830/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
+          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/news-3192/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3548680-sanjeevani-transforming-cancer-care-through-unity-and-awareness</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-proposes-to-amend-bombay-nursing-home-act-health-dept-to-hire-legal-firm/articleshow/121275842.cms</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170909/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170610/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160560/</t>
+          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157898/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173688/</t>
+          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
+          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
+          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
+          <t>https://mahasamvad.in/170909/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
+          <t>https://mahasamvad.in/170610/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
+          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
+          <t>https://mahasamvad.in/160560/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
+          <t>https://mahasamvad.in/157898/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
+          <t>https://mahasamvad.in/173688/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
+          <t>https://www.thehansindia.com/news/national/rising-gbs-cases-pune-municipal-corporation-issues-strict-regulations-for-ro-projects-946718</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
+          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
+          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/more-that-12k-children-died-in-maharashtra-between-april-last-year-and-february-2025-minister-3619100</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172749/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173717/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172235/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173797/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163359/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155268/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
+          <t>https://news.abplive.com/cities/over-14-500-women-detected-with-cancer-like-symptoms-post-screening-in-maharashtra-hingoli-1787139</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158746/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/more-that-12k-children-died-in-maharashtra-between-april-last-year-and-february-2025-minister-3619100</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166821/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155119/</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-farmers-question-mahayuti-government-over-nagpur-goa-shaktipeeth-highway-bam92</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
+          <t>https://mahasamvad.in/172749/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
+          <t>https://mahasamvad.in/173717/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
+          <t>https://mahasamvad.in/172235/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
+          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
+          <t>https://zeenews.india.com/hindi/health/first-case-of-guillain-barre-syndrome-in-mumbai-total-gbs-patient-number-180-maharashtra/2637580</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
+          <t>https://www.totaltv.in/guillain-barre-syndrome-wreaks-havoc-in-pune-patients-throng-hospitals-due-to-drinking-contaminated-water/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
+          <t>https://mahasamvad.in/173797/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
+          <t>https://mahasamvad.in/163359/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
+          <t>https://mahasamvad.in/155268/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
+          <t>https://mahasamvad.in/158746/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175429/</t>
+          <t>https://mahasamvad.in/166821/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
+          <t>https://mahasamvad.in/155119/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/12k-kid-deaths-in-11-months/articleshow/122305129.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
+          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-beed-santosh-deshmukh-case-maharashtra-politics-malegaon-sahakari-sakhar-karkhana-election-2025-1365817</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
+          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
+          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-businessman-son-died-in-horrifying-accident-with-car-expensive-bike-and-helmet-broken-into-pieces/articleshow/120491249.cms</t>
+          <t>https://www.dainikprabhat.com/maharashtra-news-hindustani-bhau-madhuri-elephant-kolhapur-vantara/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shahu-maharaj-jayanti-celebrated-with-great-enthusiasm-in-kolhapur-mp-shahu-maharaj-chhatrapati-and-sharad-pawar-pay-tribute-to-shahu-maharaj-maharashtra-news-mhs25062605058</t>
+          <t>https://medicaldialogues.in/news/health/guillain-barre-syndrome-cases-health-ministry-deploys-7-member-team-to-pune-142306</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-farmers-question-mahayuti-government-over-nagpur-goa-shaktipeeth-highway-bam92</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/03/bom5-mh-elephant-morcha.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
+          <t>https://nenow.in/national/kolhapur-residents-hold-silent-march-seek-return-of-elephant-mahadevi-from-gujarats-vantara.html</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/154371/</t>
+          <t>https://mahasamvad.in/175429/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B2%E0%A4%BE%E0%A4%A1%E0%A4%95%E0%A5%80-%E0%A4%AC%E0%A4%B9%E0%A5%80%E0%A4%A3%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%86%E0%A4%B0%E0%A5%8B%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%BE/96992/</t>
+          <t>https://www.dainikprabhat.com/vantara-and-the-state-government-will-jointly-file-a-petition-in-the-supreme-court-for-mahadevi/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
+          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161521/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/12k-kid-deaths-in-11-months/articleshow/122305129.cms</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174716/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172498/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
+          <t>https://www.expresshealthcare.in/amp/news/narayana-health-srcc-childrens-hospital-observes-world-child-obesity-day-2025-in-collaboration-with-gen-xl-foundation/449213/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171744/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/mumbai/kolhapur-rises-for-mahadevi-thousands-join-silent-march-demanding-elephants-return-from-vantara-011-7820557.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
+          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167140/</t>
+          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
+          <t>https://www.etvbharat.com/mr/!state/jyotiba-chaitra-yatra-in-the-presence-of-lakhs-of-devotees-at-jyotiba-temple-kolhapur-maharashtra-news-mhs25041203162</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
+          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
+          <t>https://www.mahasamvad.in/154371/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-government-announces-list-of-ministers-who-will-hoist-the-flag-on-august-15/</t>
+          <t>https://dainikekmat.com/%E0%A4%B2%E0%A4%BE%E0%A4%A1%E0%A4%95%E0%A5%80-%E0%A4%AC%E0%A4%B9%E0%A5%80%E0%A4%A3%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%86%E0%A4%B0%E0%A5%8B%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%BE/96992/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174988/</t>
+          <t>https://mahasamvad.in/161521/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
+          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
+          <t>https://mahasamvad.in/174716/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
+          <t>https://mahasamvad.in/172498/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
+          <t>https://medicalbuyer.co.in/maharashtra-to-launch-accreditation-system-for-private-hospitals/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/sdma-structure-to-be-changed-to-accommodate-maharashtra-deputy-cms-3400638</t>
+          <t>https://mahasamvad.in/171744/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
+          <t>https://www.msn.com/en-in/news/India/march-for-mahadevi-why-thousands-are-walking-40-km-for-an-elephant-in-kolhapur-and-how-is-vantara-involved/ar-AA1JVic0</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
+          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
+          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/three-major-issues-in-the-mahadevi-elephant-case-to-be-discussed-in-mumbai-administration-consults-legal-experts-for-further-course-of-action-srs92</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
+          <t>https://mahasamvad.in/167140/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
+          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/arogya-mitras-to-go-on-indefinite-statewide-strike-from-feb-12-101737405442305.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-instructs-to-make-special-arrangement-for-treatment-of-gbs-patients20250128191358/</t>
+          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
+          <t>https://marathi.abplive.com/news/kolhapur/chief-justice-of-india-bhushan-gavai-says-kolhapur-bench-is-a-milestone-for-social-and-economic-justice-in-the-country-will-soon-be-converted-into-a-bench-1377738</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278523385/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-acrob-india</t>
+          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
+        <is>
+          <t>https://deshdoot.com/maharashtra-government-announces-list-of-ministers-who-will-hoist-the-flag-on-august-15/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>https://pragativadi.com/first-phase-of-desh-ka-prakriti-parikshan-abhiyaan-concludes-with-historic-5-guinness-world-records/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/more-than-270-crores-due-from-mahatma-phule-and-ayushman-yojana-affiliated-hospitals-from-the-maharashtra-mahayuti-government-1352831</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>https://m.thewire.in/article/ptiprnews/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/amp?utm=relatedarticles</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/sdma-structure-to-be-changed-to-accommodate-maharashtra-deputy-cms-3400638</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/new-updates/march-for-mahadevi-why-thousands-are-walking-40-km-for-an-elephant-in-kolhapur-and-how-is-vantara-involved/articleshow/123111263.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/akola/akola-woman-hospital-nicu-tender-contract-corruption-district-surgeon-suspended-health-marathi-news-1374092</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>https://www.oneindia.com/india/maharashtra-guardian-ministers-dhananjay-munde-excluded-011-4046325.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/pune-news/arogya-mitras-to-go-on-indefinite-statewide-strike-from-feb-12-101737405442305.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-instructs-to-make-special-arrangement-for-treatment-of-gbs-patients20250128191358/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>https://www.bignewsnetwork.com/news/278523385/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-acrob-india</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
         <is>
           <t>https://mahasamvad.in/171817/</t>
         </is>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,28 +459,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maratha-reservation-news-suspend-all-the-doctors-who-came-to-conduct-the-examination-manoj-jarange-demands-health-minister-prakash-abitkar-1381217</t>
+          <t>https://www.msn.com/mr-in/news/other/gokul-%E0%A4%97-%E0%A4%95%E0%A5%81%E0%A4%B3-%E0%A4%AE%E0%A4%A7-%E0%A4%B2-%E0%A4%9C-%E0%A4%9C%E0%A4%AE-%E0%A4%98%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%B3-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%B5%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%B6%E0%A5%8D%E0%A4%B0-%E0%A4%AB-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%A8%E0%A4%B0%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%AA%E0%A5%8D%E0%A4%AA-%E0%A4%95/ar-AA1M9nH2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/rural-women-to-receive-direct-support-for-homes-and-grocery-shops-under-makan-kirana-scheme-local18-1474089.html</t>
+          <t>https://www.tarunbharat.com/ganeshotsav-2025-kolhapur-ganpati-bappa-say-goodbye-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-ganesh-visarjan-2025-emotional-child-video-bappa-immersion-anant-chaturdashi-spb94</t>
+          <t>https://www.dainikprabhat.com/the-first-ever-ganpati-visarjan-procession-in-kolhapur-begins-chants-of-ganpati-bappa-morya/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C-%E0%A4%AC-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A5%87-80-%E0%A4%AB-%E0%A4%B8%E0%A4%A6-%E0%A4%AE-%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%8F%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B8%E0%A4%AA-%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%85%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0/ar-AA1xXkGu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://news18marathi.com/maharashtra/rural-women-to-receive-direct-support-for-homes-and-grocery-shops-under-makan-kirana-scheme-local18-1474089.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-ganesh-visarjan-2025-emotional-child-video-bappa-immersion-anant-chaturdashi-spb94</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,56 +438,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Health-dept-to-probe-into-claim-about-Pune-hospital-s-refusal-to-admit-pregnant-woman/2433535</t>
+          <t>https://mandalnews.com/vidarbha/improvement-in-health-services-in-nagpur-amravati-melghat-areas/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.expresshealthcare.in/news/cii-hospital-tech-2025-to-convene-healthcare-leaders-in-mumbai-for-dialogue-on-innovation-and-health-systems/450583/</t>
+          <t>https://deshbandhump.com/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF%E0%A5%8B%E0%A4%82-%E0%A4%95%E0%A5%8B-%E0%A4%98%E0%A4%AC%E0%A4%B0%E0%A4%BE%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%80-%E0%A4%9C%E0%A4%B0%E0%A5%82/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-on-strike-ordered-to-resume-work-or-face-action-committee-decries-pressure-tactics/articleshow/123642982.cms</t>
+          <t>https://mahasamvad.in/178324/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/gokul-%E0%A4%97-%E0%A4%95%E0%A5%81%E0%A4%B3-%E0%A4%AE%E0%A4%A7-%E0%A4%B2-%E0%A4%9C-%E0%A4%9C%E0%A4%AE-%E0%A4%98%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%B3-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%B5%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%B6%E0%A5%8D%E0%A4%B0-%E0%A4%AB-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%A8%E0%A4%B0%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%AA%E0%A5%8D%E0%A4%AA-%E0%A4%95/ar-AA1M9nH2</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/nhm-strike-ends-health-minister-promises-demands-135887825.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ganeshotsav-2025-kolhapur-ganpati-bappa-say-goodbye-marathi-news/</t>
+          <t>https://mahasamvad.in/178441/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/the-first-ever-ganpati-visarjan-procession-in-kolhapur-begins-chants-of-ganpati-bappa-morya/</t>
+          <t>https://www.mahasamvad.in/178397/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/rural-women-to-receive-direct-support-for-homes-and-grocery-shops-under-makan-kirana-scheme-local18-1474089.html</t>
+          <t>https://www.mahasamvad.in/page/4/?m=0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-ganesh-visarjan-2025-emotional-child-video-bappa-immersion-anant-chaturdashi-spb94</t>
+          <t>https://www.esakal.com/amp/pimpri-chinchwad/todays-latest-marathi-news-pne25l38633-txt-pc-today-20250914110635</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/amp/health/body-gives-you-these-two-warning-signs-before-paralysis-attack-never-ignore-stroke-symptoms-ssg2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/amp/uttar-maharashtra/jalgaon-viral-infections-post-rainfall-respiratory-illness-hospitals-patient-surge-nmk01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/amp/ahmednagar/container-with-brake-failure-crushes-9-vehicles-in-ahilyanagar-truck-accident-vru98</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.tarunbharat.com/kolhapur-haddwadh-process-stopped-question-to-guardian-minister-marathi-news/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-call-off-strike-after-health-ministers-assurances/amp_articleshow/123816244.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/mla-amashya-padvi-warning-to-government-over-reservation-for-banjara-and-dhangar-communities-maharashtra-news-mhs25091308686</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://deshonnati.com/nhm-employees-strike-finally-called-off/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/special-news/rahul-gandhi-said-on-pm-modis-visit-to-manipur-its-ok-but-main-issue-is-vote-theft/?noamp=mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-live-news-13th-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-local-train-block-uddhav-thackeray-cm-devendra-fadnavis/liveblog/123862426.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.tarunbharat.com/ganeshotsav-2025-kolhapur-ganpati-bappa-say-goodbye-marathi-news/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/amp/premier/naam-foundation-celebrates-its-10th-anniversary-in-presence-of-minitster-nitin-gadkari-entertainment-news-kds07</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C-%E0%A4%AC-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A5%87-80-%E0%A4%AB-%E0%A4%B8%E0%A4%A6-%E0%A4%AE-%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%8F%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B8%E0%A4%AA-%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%85%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0/ar-AA1xXkGu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,140 +438,189 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/vidarbha/improvement-in-health-services-in-nagpur-amravati-melghat-areas/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/abitkar-bats-for-state-level-wild-egetable-festival/articleshow/124003944.cms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF%E0%A5%8B%E0%A4%82-%E0%A4%95%E0%A5%8B-%E0%A4%98%E0%A4%AC%E0%A4%B0%E0%A4%BE%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%80-%E0%A4%9C%E0%A4%B0%E0%A5%82/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178324/</t>
+          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/nhm-strike-ends-health-minister-promises-demands-135887825.html</t>
+          <t>https://www.newsdrum.in/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pms-birthday-10474617</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178441/</t>
+          <t>https://mandalnews.com/amravati/beds-are-lying-vacant-in-super-specialty-hospital/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/178397/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/4/?m=0</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%9A-%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%B2%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%9D-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%B8-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%9C%E0%A4%A8%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0-%E0%A4%95%E0%A4%B0/ar-AA1DlKs7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/pimpri-chinchwad/todays-latest-marathi-news-pne25l38633-txt-pc-today-20250914110635</t>
+          <t>https://mahasamvad.in/178819/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/health/body-gives-you-these-two-warning-signs-before-paralysis-attack-never-ignore-stroke-symptoms-ssg2</t>
+          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/uttar-maharashtra/jalgaon-viral-infections-post-rainfall-respiratory-illness-hospitals-patient-surge-nmk01</t>
+          <t>https://www.tarunbharat.com/jay-kumar-gore-says-true-strength-lies-in-the-coordination-village-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/ahmednagar/container-with-brake-failure-crushes-9-vehicles-in-ahilyanagar-truck-accident-vru98</t>
+          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-haddwadh-process-stopped-question-to-guardian-minister-marathi-news/</t>
+          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-call-off-strike-after-health-ministers-assurances/amp_articleshow/123816244.cms</t>
+          <t>https://mandalnews.com/amravati/sulabha-khodkes-initiative-resolved-the-issue-of-strike-by-super-specialty-doctors/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mla-amashya-padvi-warning-to-government-over-reservation-for-banjara-and-dhangar-communities-maharashtra-news-mhs25091308686</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/abitkar-bats-for-state-level-wild-egetable-festival/amp_articleshow/124003944.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/nhm-employees-strike-finally-called-off/</t>
+          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/special-news/rahul-gandhi-said-on-pm-modis-visit-to-manipur-its-ok-but-main-issue-is-vote-theft/?noamp=mobile</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-live-news-13th-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-local-train-block-uddhav-thackeray-cm-devendra-fadnavis/liveblog/123862426.cms</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ganeshotsav-2025-kolhapur-ganpati-bappa-say-goodbye-marathi-news/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/premier/naam-foundation-celebrates-its-10th-anniversary-in-presence-of-minitster-nitin-gadkari-entertainment-news-kds07</t>
+          <t>https://mahasamvad.in/179319/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C-%E0%A4%AC-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A5%87-80-%E0%A4%AB-%E0%A4%B8%E0%A4%A6-%E0%A4%AE-%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%8F%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B8%E0%A4%AA-%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%85%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0/ar-AA1xXkGu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/mr-in/news/other/guillain-barre-syndrome-%E0%A4%97-%E0%A4%AF-%E0%A4%AC-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%A1%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A4%B9%E0%A4%B0-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%B8%E0%A4%82%E0%A4%96%E0%A5%8D%E0%A4%AF-130-%E0%A4%B5%E0%A4%B0/ar-AA1y9GYn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/maharashtra/government-fund-for-treatments-above-5-lakh-number-of-beneficiaries-to-increase-cm-devendra-fadnavis-pjp78</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/178534/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/178863/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,182 +445,154 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
+          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pms-birthday-10474617</t>
+          <t>https://mandalnews.com/amravati/beds-are-lying-vacant-in-super-specialty-hospital/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/beds-are-lying-vacant-in-super-specialty-hospital/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://mahasamvad.in/178819/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%9A-%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%B2%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%9D-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%B8-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%9C%E0%A4%A8%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0-%E0%A4%95%E0%A4%B0/ar-AA1DlKs7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178819/</t>
+          <t>https://www.tarunbharat.com/jay-kumar-gore-says-true-strength-lies-in-the-coordination-village-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/jay-kumar-gore-says-true-strength-lies-in-the-coordination-village-marathi-news/</t>
+          <t>https://lokashanews.com/28208/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
+          <t>https://mahasamvad.in/178863/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
+          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/sulabha-khodkes-initiative-resolved-the-issue-of-strike-by-super-specialty-doctors/</t>
+          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/abitkar-bats-for-state-level-wild-egetable-festival/amp_articleshow/124003944.cms</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
+          <t>https://mahasamvad.in/179319/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%A4-%E0%A4%95-%E0%A4%9A%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%95%E0%A4%AA-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%9A%E0%A4%B9-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%95%E0%A4%AA%E0%A4%B9-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%B9%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A4%AA-%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A5%87%E0%A4%A4/ar-BB1r7UnW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://www.esakal.com/maharashtra/government-fund-for-treatments-above-5-lakh-number-of-beneficiaries-to-increase-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179319/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/guillain-barre-syndrome-%E0%A4%97-%E0%A4%AF-%E0%A4%AC-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%A1%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A4%B9%E0%A4%B0-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%B8%E0%A4%82%E0%A4%96%E0%A5%8D%E0%A4%AF-130-%E0%A4%B5%E0%A4%B0/ar-AA1y9GYn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/government-fund-for-treatments-above-5-lakh-number-of-beneficiaries-to-increase-cm-devendra-fadnavis-pjp78</t>
+          <t>https://mahasamvad.in/178534/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
+          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178534/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178863/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
           <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,21 +452,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/beds-are-lying-vacant-in-super-specialty-hospital/</t>
+          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://mandalnews.com/amravati/beds-are-lying-vacant-in-super-specialty-hospital/</t>
         </is>
       </c>
     </row>
@@ -487,14 +487,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/jay-kumar-gore-says-true-strength-lies-in-the-coordination-village-marathi-news/</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.mahasamvad.in/page/45/?m=0</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178863/</t>
+          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
         </is>
       </c>
     </row>
@@ -536,63 +536,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179319/</t>
+          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%A4-%E0%A4%95-%E0%A4%9A%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%95%E0%A4%AA-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%9A%E0%A4%B9-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%95%E0%A4%AA%E0%A4%B9-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%B9%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A4%AA-%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A5%87%E0%A4%A4/ar-BB1r7UnW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://mahasamvad.in/179319/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/government-fund-for-treatments-above-5-lakh-number-of-beneficiaries-to-increase-cm-devendra-fadnavis-pjp78</t>
+          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
+          <t>https://mahasamvad.in/178534/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178534/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
+          <t>https://mahasamvad.in/178863/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,21 +445,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/45/?m=0</t>
+          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
         </is>
       </c>
     </row>
@@ -529,56 +529,49 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://mahasamvad.in/179319/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179319/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178534/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178863/</t>
+          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,14 +445,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178819/</t>
+          <t>https://hindi.oneindia.com/news/india/shiv-sena-celebrates-pm-narendra-modi-birthday-initiatives-011-1388481.html</t>
         </is>
       </c>
     </row>
@@ -487,70 +487,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://lokashanews.com/28208/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
+          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28208/</t>
+          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-advocate-general-birendra-saraf-resigns-will-continue-his-work-till-january/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
+          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://civicmirror.in/maharashtra/paint-thrown-on-meenatai-thackerays-statue-in-mumbai-shiv-sena-aggressive/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-cabinet-meeting-cabinet-approves-states-new-gaming-policy-know-8-major-decisions-from-the-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179319/</t>
+          <t>https://civicmirror.in/maharashtra/now-the-licenses-of-vehicles-transporting-sand-illegally-will-be-suspended-a-strict-decision-by-the-transport-department/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
+          <t>https://civicmirror.in/maharashtra/will-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-in-august-and-september-agriculture-minister-dattatreya-bharane/</t>
         </is>
       </c>
     </row>
@@ -564,14 +564,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links_Prakash Abitkar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,14 +445,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
         </is>
       </c>
     </row>
@@ -487,28 +487,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28208/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
+          <t>https://lokashanews.com/28208/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
+          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-advocate-general-birendra-saraf-resigns-will-continue-his-work-till-january/</t>
+          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>
@@ -522,47 +522,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/paint-thrown-on-meenatai-thackerays-statue-in-mumbai-shiv-sena-aggressive/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-cabinet-meeting-cabinet-approves-states-new-gaming-policy-know-8-major-decisions-from-the-cabinet-meeting/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/now-the-licenses-of-vehicles-transporting-sand-illegally-will-be-suspended-a-strict-decision-by-the-transport-department/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/will-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-in-august-and-september-agriculture-minister-dattatreya-bharane/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
         <is>
           <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
